--- a/Procedure and Memo.xlsx
+++ b/Procedure and Memo.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC80CE2-4755-40A1-BFE9-3F74CB9EC3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Procedure" sheetId="1" r:id="rId1"/>
+    <sheet name="Memo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,15 +25,964 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>student</author>
+    <author>tc={CB758F7F-81AD-4C74-8478-87E8CA61F05B}</author>
+  </authors>
+  <commentList>
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{643D890D-B599-4F1F-95C2-016439C9EC1D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="2"/>
+          </rPr>
+          <t>student:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L56" authorId="1" shapeId="0" xr:uid="{CB758F7F-81AD-4C74-8478-87E8CA61F05B}">
+      <text>
+        <t xml:space="preserve">[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    tep 3 — Create a new app registration
+Once logged in to entra.microsoft.com:
+Look at the left sidebar
+Find and click "Applications"
+Click "App registrations"
+Click "+ New registration"
+Step 4 — Fill in the registration form
+Name: receipt-automation-pipeline
+Supported account types: select "Personal Microsoft accounts only"
+Redirect URI: 
+Select "Web" from the dropdown
+Type: http://localhost:8080
+Click "Register"
+Step 5 — Copy your App IDs
+On your app page you should see:
+Application (client) ID
+Directory (tenant) ID
+Copy both of these values and paste them somewhere safe (like a notepad) for now.
+Step 6 — Create a Client Secret
+On the left sidebar click "Certificates &amp; secrets"
+Click "+ New client secret"
+Fill in: 
+Description: receipt-secret
+Expires: choose 24 months
+Click "Add"
+You will see a new row appear with a Value column.
+⚠️ Copy the Value immediately! It will be hidden after you leave this page and you can never see it again.
+Paste all three values in your notepad:
+CLIENT_ID = (Application client ID) TENANT_ID = (Directory tenant ID) CLIENT_SECRET = (the secret Value you just copied)
+Tell me when you have all three saved!
+Step 7 — Add API Permissions
+On the left sidebar:
+Click "API permissions"
+Click "+ Add a permission"
+Click "Microsoft Graph"
+Click "Delegated permissions"
+In the search box type Mail.Read
+Check the box next to Mail.Read
+Click "Add permissions"
+Step 8 — Add one more permission
+Repeat the same steps:
+Click "+ Add a permission"
+Click "Microsoft Graph"
+Click "Delegated permissions"
+Search for offline_access
+Check the box next to offline_access
+Click "Add permissions"
+You should now see two permissions in your list:
+✅ Mail.Read ✅ offline_access
+Tell me when you see both permissions added!
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+  <si>
+    <t>created the path C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>set up a virtual environment (python) \venv\Scripts\activate</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>added additional packet  pip install requests msal gspread google-auth streamlit pandas</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#pandas is installed </t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>requests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Used to send commands to a website or API (e.g., retrieving data from the web or sending data elsewhere).</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>msal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: (Microsoft Authentication Library) Used for logging into Microsoft systems, such as connecting to Outlook, SharePoint, or Azure.</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gspread</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Used specifically for reading and writing data in Google Sheets.</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>google-auth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Used to manage Google permissions and authentication for secure access to Google Sheets or Google Drive.</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>streamlit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Used to quickly transform Python code into beautiful web apps or dashboards (very popular in data science).</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pandas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Used to manage and analyze data in tabular format (similar to Excel but works through code).</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Create project files</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>.env</t>
+  </si>
+  <si>
+    <t>.env.example</t>
+  </si>
+  <si>
+    <t>requirements.txt</t>
+  </si>
+  <si>
+    <t>src/email_fetcher.py</t>
+  </si>
+  <si>
+    <t>src/parser.py</t>
+  </si>
+  <si>
+    <t>src/sheets_writer.py</t>
+  </si>
+  <si>
+    <t>dashboard/app.py</t>
+  </si>
+  <si>
+    <t>Set up the templete shows what credential are needed  in .env.example</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t># Microsoft Graph API</t>
+  </si>
+  <si>
+    <t>CLIENT_ID=your_client_id_here</t>
+  </si>
+  <si>
+    <t>CLIENT_SECRET=your_client_secret_here</t>
+  </si>
+  <si>
+    <t>TENANT_ID=your_tenant_id_here</t>
+  </si>
+  <si>
+    <t>EMAIL=your_email@hotmail.com</t>
+  </si>
+  <si>
+    <t># Google Sheets</t>
+  </si>
+  <si>
+    <t>GOOGLE_SHEET_NAME=your_sheet_name_here</t>
+  </si>
+  <si>
+    <t>Create .gitgnore to ignore .evn and venv</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>venv/</t>
+  </si>
+  <si>
+    <t>__pycache__/</t>
+  </si>
+  <si>
+    <t>*.pyc</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ไฟล์</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> env.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> คือไฟล์ที่เอาไวเก็บความลับห้ามบอกคนอื่นห้ามอัพลง เช่น </t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Password </t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>API key</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ไฟล์</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> env.example</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> เอาไว้เป็น </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">templete </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">ของ  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.env</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> เอาไว้ให้คนอื่นดู</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>GOOGLE_SHEET_ID=your_id_here</t>
+  </si>
+  <si>
+    <t>MS_CLIENT_ID=your_client_id_here</t>
+  </si>
+  <si>
+    <t>sign in with my oamplove5@hotmail.com account.</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Access to Microsoft Entra by  https://entra.microsoft.com  </t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Microsoft Entra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>การระบุตัวตนและการเข้าถึงเครือข่าย</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Told Microsoft "this script has permission to read emails from this Hotmail account". The CLIENT_ID, CLIENT_SECRET, TENANT_ID are like a username/password for your app.</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>install 0365 via powershell</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Mail.Read  = Python can read emails</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>offline_access = Python can stay connected without logging in every time</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Added API Permission Mail.Read &amp; offline_access. Let my app can read the email</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>สร้างสภาพแวดล้อมเสมือน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(venv)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>พื้นที่ทำงาน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ที่แยกต่างหากสำหรับโปรเจกต์นี้โดยเฉพาะ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ช่วยให้ไลบรารีต่างๆ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>แยกจากโปรเจกต์อื่นๆ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>บนคอมพิวเตอร์ของคุณ</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>requests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>msal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — talk to Microsoft APIs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>O365</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — simplified library to connect to Outlook/Hotmail</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>gspread</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>google-auth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — read/write Google Sheets</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>streamlit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>pandas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — dashboard and data handling</t>
+    </r>
+  </si>
+  <si>
+    <t>Use o365 to conect Outlook for API read mail</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>dotenv fetch API Key ,Client ID, Client Secret, Database password</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">.env = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ตู้เซฟเก็บความลับ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dotenv = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>กุญแจเปิดตู้</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">os.getenv = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>หยิบของออกมาใช้</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dotenv </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ไว้ดึง</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> .evn</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>scopes</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>These are the permissions we requested from Microsoft.
+'basic' → Basic account information
+'message_all' → Access to all emails</t>
+    <phoneticPr fontId="3"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,11 +1005,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -66,6 +1037,345 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>182881</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>91149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9B1B967-85BB-4B0E-BEFD-E641304A54BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="670561" y="2971800"/>
+          <a:ext cx="2194560" cy="1691349"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>83970</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7375BFA2-BB8E-4F6A-A9AC-B66A581F045E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2697480" y="4884420"/>
+          <a:ext cx="2278380" cy="1600350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15241</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>54202</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>53341</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>150631</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F45361AA-4174-4D16-89C1-5D527673147E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685801" y="10341202"/>
+          <a:ext cx="5402580" cy="1925229"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>450155</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>99786</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14640834-797C-94DD-C27F-A1F74FADD883}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="693420" y="10157460"/>
+          <a:ext cx="5791775" cy="1143726"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>30481</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>651473</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>60961</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E752869B-96C2-9366-4B68-31DF30F8858E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="708660" y="15118081"/>
+          <a:ext cx="5307293" cy="716280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>548641</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>154283</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8073CD51-CE55-D9D8-1C39-20159332377A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="670561" y="16459200"/>
+          <a:ext cx="3901440" cy="2440283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="SOMBUD　AUMPON" id="{E274DEFF-D9F5-4B46-A727-BA60BE33EBF1}" userId="S::251013@st.yoshida-g.ac.jp::8eaaffbe-8849-44aa-b0da-ff1ee440ce1c" providerId="AD"/>
+</personList>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -329,11 +1639,479 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="L56" dT="2026-03-03T13:08:46.28" personId="{E274DEFF-D9F5-4B46-A727-BA60BE33EBF1}" id="{CB758F7F-81AD-4C74-8478-87E8CA61F05B}">
+    <text xml:space="preserve">tep 3 — Create a new app registration
+Once logged in to entra.microsoft.com:
+Look at the left sidebar
+Find and click "Applications"
+Click "App registrations"
+Click "+ New registration"
+Step 4 — Fill in the registration form
+Name: receipt-automation-pipeline
+Supported account types: select "Personal Microsoft accounts only"
+Redirect URI: 
+Select "Web" from the dropdown
+Type: http://localhost:8080
+Click "Register"
+Step 5 — Copy your App IDs
+On your app page you should see:
+Application (client) ID
+Directory (tenant) ID
+Copy both of these values and paste them somewhere safe (like a notepad) for now.
+Step 6 — Create a Client Secret
+On the left sidebar click "Certificates &amp; secrets"
+Click "+ New client secret"
+Fill in: 
+Description: receipt-secret
+Expires: choose 24 months
+Click "Add"
+You will see a new row appear with a Value column.
+⚠️ Copy the Value immediately! It will be hidden after you leave this page and you can never see it again.
+Paste all three values in your notepad:
+CLIENT_ID = (Application client ID) TENANT_ID = (Directory tenant ID) CLIENT_SECRET = (the secret Value you just copied)
+Tell me when you have all three saved!
+Step 7 — Add API Permissions
+On the left sidebar:
+Click "API permissions"
+Click "+ Add a permission"
+Click "Microsoft Graph"
+Click "Delegated permissions"
+In the search box type Mail.Read
+Check the box next to Mail.Read
+Click "Add permissions"
+Step 8 — Add one more permission
+Repeat the same steps:
+Click "+ Add a permission"
+Click "Microsoft Graph"
+Click "Delegated permissions"
+Search for offline_access
+Check the box next to offline_access
+Click "Add permissions"
+You should now see two permissions in your list:
+✅ Mail.Read ✅ offline_access
+Tell me when you see both permissions added!
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L88"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="B3" s="3" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1"/>
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1"/>
+      <c r="B10" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1"/>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12"/>
+    <row r="56" spans="1:12"/>
+    <row r="62" spans="1:12">
+      <c r="B62" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64">
+        <v>9</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="B65" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="B66" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>10</v>
+      </c>
+      <c r="B71" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="B84" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="B85" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="B86" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:H5"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF3FDBC-99E4-40E5-AA7C-C0AF768B925F}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Procedure and Memo.xlsx
+++ b/Procedure and Memo.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC80CE2-4755-40A1-BFE9-3F74CB9EC3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C7F393-042F-4EEE-ABFD-E9D97B932687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Procedure" sheetId="1" r:id="rId1"/>
     <sheet name="Memo" sheetId="2" r:id="rId2"/>
+    <sheet name="Troubleshooting" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -141,22 +142,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
   <si>
     <t>created the path C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>set up a virtual environment (python) \venv\Scripts\activate</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>added additional packet  pip install requests msal gspread google-auth streamlit pandas</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">#pandas is installed </t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -181,7 +182,7 @@
       </rPr>
       <t>: Used to send commands to a website or API (e.g., retrieving data from the web or sending data elsewhere).</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -206,7 +207,7 @@
       </rPr>
       <t>: (Microsoft Authentication Library) Used for logging into Microsoft systems, such as connecting to Outlook, SharePoint, or Azure.</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -231,7 +232,7 @@
       </rPr>
       <t>: Used specifically for reading and writing data in Google Sheets.</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -256,7 +257,7 @@
       </rPr>
       <t>: Used to manage Google permissions and authentication for secure access to Google Sheets or Google Drive.</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -281,7 +282,7 @@
       </rPr>
       <t>: Used to quickly transform Python code into beautiful web apps or dashboards (very popular in data science).</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -306,11 +307,11 @@
       </rPr>
       <t>: Used to manage and analyze data in tabular format (similar to Excel but works through code).</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Create project files</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>.env</t>
@@ -335,7 +336,7 @@
   </si>
   <si>
     <t>Set up the templete shows what credential are needed  in .env.example</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t># Microsoft Graph API</t>
@@ -360,7 +361,7 @@
   </si>
   <si>
     <t>Create .gitgnore to ignore .evn and venv</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>venv/</t>
@@ -402,15 +403,15 @@
       </rPr>
       <t xml:space="preserve"> คือไฟล์ที่เอาไวเก็บความลับห้ามบอกคนอื่นห้ามอัพลง เช่น </t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">Password </t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>API key</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -483,7 +484,7 @@
       </rPr>
       <t xml:space="preserve"> เอาไว้ให้คนอื่นดู</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>GOOGLE_SHEET_ID=your_id_here</t>
@@ -493,11 +494,11 @@
   </si>
   <si>
     <t>sign in with my oamplove5@hotmail.com account.</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">Access to Microsoft Entra by  https://entra.microsoft.com  </t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -513,27 +514,27 @@
       </rPr>
       <t>การระบุตัวตนและการเข้าถึงเครือข่าย</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Told Microsoft "this script has permission to read emails from this Hotmail account". The CLIENT_ID, CLIENT_SECRET, TENANT_ID are like a username/password for your app.</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>install 0365 via powershell</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Mail.Read  = Python can read emails</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>offline_access = Python can stay connected without logging in every time</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Added API Permission Mail.Read &amp; offline_access. Let my app can read the email</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -665,7 +666,7 @@
       </rPr>
       <t>บนคอมพิวเตอร์ของคุณ</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -786,11 +787,11 @@
   </si>
   <si>
     <t>Use o365 to conect Outlook for API read mail</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>dotenv fetch API Key ,Client ID, Client Secret, Database password</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -860,17 +861,129 @@
       </rPr>
       <t xml:space="preserve"> .evn</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>scopes</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>These are the permissions we requested from Microsoft.
 'basic' → Basic account information
 'message_all' → Access to all emails</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Real problems encountered during development and how they were solved</t>
+  </si>
+  <si>
+    <t>Problem 1 — School tenant blocked personal account</t>
+  </si>
+  <si>
+    <t>**Error:**</t>
+  </si>
+  <si>
+    <t>```</t>
+  </si>
+  <si>
+    <t>AADSTS90072: User account does not exist in tenant 'yoshida-g.ac.jp'</t>
+  </si>
+  <si>
+    <t>**Cause:** Computer was linked to school Microsoft account, so Azure</t>
+  </si>
+  <si>
+    <t>kept logging in with school account instead of personal Hotmail.</t>
+  </si>
+  <si>
+    <r>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fix:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD3D7DE"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Opened Azure portal in Incognito browser and signed in manually with personal Hotmail account. </t>
+    </r>
+  </si>
+  <si>
+    <t>Invalid redirect URI</t>
+  </si>
+  <si>
+    <t>invalid_request: The provided value for the input parameter</t>
+  </si>
+  <si>
+    <t>'redirect_uri' is not valid</t>
+  </si>
+  <si>
+    <t>**Cause:** Used `http://localhost:8080` which works for Web apps</t>
+  </si>
+  <si>
+    <t>but not for personal Microsoft accounts.</t>
+  </si>
+  <si>
+    <t>**Fix:** Changed platform from Web to Mobile and desktop applications</t>
+  </si>
+  <si>
+    <t>in Azure Authentication settings and used:</t>
+  </si>
+  <si>
+    <t>https://login.microsoftonline.com/common/oauth2/nativeclient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authentication is completed. O365 token is stored. Now can use API my script can now talk to  Hotmail inbox! </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">**Cause:** Browser was redirecting to "wrongplace" page and </t>
+  </si>
+  <si>
+    <t>the ?code= token was in a different browser tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Fix:** After login, check ALL open browser tabs for the one </t>
+  </si>
+  <si>
+    <t xml:space="preserve">containing ?code= in the address bar. Copy that full URL and </t>
+  </si>
+  <si>
+    <t>paste into terminal when prompted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Redirect URL not capturing ?code=</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">fetch the mail outlook and print for a test </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>*please note I have the email box that named "Yucho" for store receive only the receipts for using debit card.</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -878,13 +991,6 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="15">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -984,6 +1090,14 @@
       <family val="2"/>
       <charset val="222"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD3D7DE"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1013,15 +1127,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1297,6 +1411,398 @@
         <a:xfrm>
           <a:off x="670561" y="16459200"/>
           <a:ext cx="3901440" cy="2440283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>427048</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>22921</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA55AF8-D648-FA77-1572-B0212FD71A90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1341120" y="20345400"/>
+          <a:ext cx="3779848" cy="708721"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1277D265-4A1D-6703-2F02-7A962287AE6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="777240" y="21640800"/>
+          <a:ext cx="4663440" cy="906780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Check point</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Authentication Flow Completed</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>— Microsoft accepted  login</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Oauth Access Token Stored</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>— Token saved to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>o365_token.txt</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t> file</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Connected successfully!</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>— Python is connected to your Hotmail</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>41868</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>495901</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>23234</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{030A6989-59BD-A5F6-D0CC-BE025D83E8F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="712428" y="23492460"/>
+          <a:ext cx="3806833" cy="2362574"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>260526</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>58133</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBACFFE3-EF06-1216-8028-EBD2715D0580}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4954446" y="23553420"/>
+          <a:ext cx="3877134" cy="2336513"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>269135</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>523663</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD758B08-68A8-A02E-4FAE-ADB748EB1DFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7645295" y="312420"/>
+          <a:ext cx="4948448" cy="2057400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>43662</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>412517</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>168075</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E2DA479-776A-3BB0-C16F-BDF267C4F624}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5151120" y="6444462"/>
+          <a:ext cx="4649237" cy="1953213"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1699,7 +2205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1719,34 +2225,34 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="3" t="e" vm="1">
+      <c r="B3" s="8" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
@@ -1763,34 +2269,34 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1"/>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1"/>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1985,20 +2491,36 @@
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="B86" s="9" t="s">
+      <c r="B86" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
         <v>11</v>
+      </c>
+      <c r="B88" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="B102" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:H5"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -2014,7 +2536,7 @@
       <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2032,12 +2554,12 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2058,27 +2580,27 @@
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2086,7 +2608,7 @@
       <c r="A13">
         <v>5</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2111,7 +2633,169 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{135E358C-4BFD-4CD4-ABD8-EC5636D7275B}">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" s="9"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="9"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="B27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Procedure and Memo.xlsx
+++ b/Procedure and Memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C7F393-042F-4EEE-ABFD-E9D97B932687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75453249-A533-428B-9D3D-EB52729041F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="89">
   <si>
     <t>created the path C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline</t>
     <phoneticPr fontId="2"/>
@@ -983,6 +983,34 @@
   </si>
   <si>
     <t>*please note I have the email box that named "Yucho" for store receive only the receipts for using debit card.</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Extract data with Regex! -</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>I write parser.py — the code that reads the email body and pulls out the 5 fields we need.</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">利用日時  </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">利用金額  </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">利用通貨  </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">承認番号  </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">利用店舗  </t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1132,10 +1160,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1466,15 +1494,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1489,7 +1517,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="777240" y="21640800"/>
+          <a:off x="792480" y="26068020"/>
           <a:ext cx="4663440" cy="906780"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1710,6 +1738,50 @@
         <a:xfrm>
           <a:off x="4954446" y="23553420"/>
           <a:ext cx="3877134" cy="2336513"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>133164</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>290201</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>84148</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F83065D-7972-680B-C21D-7A1A4EF0AD62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1474284" y="27782520"/>
+          <a:ext cx="3509837" cy="1791028"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2205,7 +2277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2225,34 +2297,34 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="8" t="e" vm="1">
+      <c r="B3" s="9" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
@@ -2514,6 +2586,44 @@
     <row r="102" spans="1:2">
       <c r="B102" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>13</v>
+      </c>
+      <c r="B120" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="B121" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="B122" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="B123" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="B124" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="B125" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="B126" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2682,15 +2792,15 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="B11" s="9"/>
+      <c r="B11" s="8"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="B12" s="9"/>
+      <c r="B12" s="8"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">

--- a/Procedure and Memo.xlsx
+++ b/Procedure and Memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75453249-A533-428B-9D3D-EB52729041F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1411239A-5EA6-4C75-B9EB-08EE920F0DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
   <si>
     <t>created the path C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline</t>
     <phoneticPr fontId="2"/>
@@ -1013,12 +1013,395 @@
     <t xml:space="preserve">利用店舗  </t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>Open google sheet Add these</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>rename sheet to "Receipt Tracker"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Data</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Time</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Store</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Amount</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>go to google cloud "https://console.cloud.google.com"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>create a new project nemed  "receipt-automation"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Click "Google Sheets API" from results Click "Enable"</t>
+  </si>
+  <si>
+    <t>Click "Google Drive API" from results Click "Enable"</t>
+  </si>
+  <si>
+    <t>Enable Google Sheets API</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Enable Google Drive API</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Google Sheets API  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ทำให้เข้าถึงข้อมูล</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t>Google Sheets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ได้</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>จัดการข้อมูล</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>อ่านและเขียนค่าในเซลล์</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>เพิ่มแถว</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Append), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>หรือลบข้อมูลในระดับช่วง</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Range).</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>Google Drive API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> เข้าถึง</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> GOOGLE DRIVE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ได้</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>จัดการไฟล์</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>อัปโหลด</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (Upload), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ดาวน์โหลด</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (Download), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ค้นหา</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (Search), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>และลบไฟล์</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Create Service Account</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name "receipt-automation"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Click "Service Accounts" from results</t>
+  </si>
+  <si>
+    <t>Click "+ Create Service Account"</t>
+  </si>
+  <si>
+    <t>Create a Key for the Service Account</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Click on the service account email to open it</t>
+  </si>
+  <si>
+    <t>Click the "Keys" tab at the top</t>
+  </si>
+  <si>
+    <t>Click "Add Key" → "Create new key"</t>
+  </si>
+  <si>
+    <t>Select "JSON"</t>
+  </si>
+  <si>
+    <t>Click "Create"</t>
+  </si>
+  <si>
+    <t>Share Google Sheet with the Service Account</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Change permission to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Editor"</t>
+    </r>
+  </si>
+  <si>
+    <t>install " pip install gspread google-auth"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">add sheets_writer.py for write on the google sheet automaticlly </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Run sheets_writer.py Google Sheets updated automatically</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>automation pipeline working truly</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1125,6 +1508,19 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1495,13 +1891,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1662,13 +2058,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>41868</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>175260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>495901</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>23234</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1706,13 +2102,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>260526</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>58133</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1750,13 +2146,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>133164</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>290201</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>84148</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1782,6 +2178,270 @@
         <a:xfrm>
           <a:off x="1474284" y="27782520"/>
           <a:ext cx="3509837" cy="1791028"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>24152</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAC0DE12-0697-6AD3-92ED-68289F95744A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="30693360"/>
+          <a:ext cx="4427220" cy="1563392"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>221926</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>275309</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>84210</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB32E1E2-1827-6EC4-B59A-5679DBB59F85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="777240" y="31997326"/>
+          <a:ext cx="4862549" cy="1919684"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15241</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>182881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>320040</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>154054</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1A9FCB6-8F3E-DD63-CB78-9D236663D6DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685801" y="36758881"/>
+          <a:ext cx="4328159" cy="2028573"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533401</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>533401</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>224436</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE5DAA5-2F9B-B532-CC5C-3C8D4A5D6F5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3886201" y="39448740"/>
+          <a:ext cx="3352800" cy="1695096"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>79110</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E2C678A-59DF-A0F7-A64E-9CEAA348DBC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="777240" y="42717720"/>
+          <a:ext cx="5173980" cy="2395590"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>209</xdr:row>
+      <xdr:rowOff>199022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F937279C-1421-3A30-FBCE-8B0883699F35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="701040" y="46352460"/>
+          <a:ext cx="5394960" cy="1623962"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2277,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:L202"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2575,55 +3235,222 @@
         <v>73</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
-      <c r="A101">
+    <row r="95" spans="1:2">
+      <c r="A95">
         <v>12</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B95" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
-      <c r="B102" t="s">
+    <row r="96" spans="1:2">
+      <c r="B96" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
-      <c r="A120">
+    <row r="114" spans="1:6">
+      <c r="A114">
         <v>13</v>
       </c>
+      <c r="B114" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="B115" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="B117" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="B120" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="B121" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="B122" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="B123" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="B124" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125">
+        <v>14</v>
+      </c>
       <c r="B125" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="B126" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" t="s">
+        <v>91</v>
+      </c>
+      <c r="C128" t="s">
+        <v>92</v>
+      </c>
+      <c r="D128" t="s">
+        <v>93</v>
+      </c>
+      <c r="E128" t="s">
+        <v>94</v>
+      </c>
+      <c r="F128" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="B139" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>16</v>
+      </c>
+      <c r="B151" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="B153" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>17</v>
+      </c>
+      <c r="B155" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="B157" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>18</v>
+      </c>
+      <c r="B159" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="B160" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="B161" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="B162" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>19</v>
+      </c>
+      <c r="B174" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="B175" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="B176" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="B177" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="B178" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="B179" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>20</v>
+      </c>
+      <c r="B183" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="B184" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>21</v>
+      </c>
+      <c r="B186" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>22</v>
+      </c>
+      <c r="B199" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>23</v>
+      </c>
+      <c r="B201" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="B202" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2639,7 +3466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF3FDBC-99E4-40E5-AA7C-C0AF768B925F}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2737,9 +3564,30 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="B18" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>7</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Procedure and Memo.xlsx
+++ b/Procedure and Memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1411239A-5EA6-4C75-B9EB-08EE920F0DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F35DA83-8019-4178-99EF-6981510E8061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="142">
   <si>
     <t>created the path C:\Users\student\Desktop\Portfolio\Receipt-Automation-Pipeline</t>
     <phoneticPr fontId="2"/>
@@ -1396,12 +1396,638 @@
     <t>automation pipeline working truly</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>Github Action start!</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GitHub Actions</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ช่วยให้คุณสามารถสั่งให้โค้ดทำงานบางอย่างโดยอัตโนมัติเมื่อเกิดเหตุการณ์</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Events) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ต่างๆ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ใน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Repository </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ของคุณ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Facebook
+Facebook
+ +3</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ระบบที่เอาไว้เก็บข้อมูลที่มีความสำคัญสูงหรือข้อมูลที่เป็น</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ความลับ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" (Sensitive information) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>เช่น</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">API Keys, Passwords, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>หรือ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tokens </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ต่างๆ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ที่เราต้องใช้ใน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">GitHub Actions </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>แต่ไม่อยากเขียนลงไปในโค้ดตรงๆ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Hardcode) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>เพราะจะทำให้คนอื่นเห็นได้ครับ</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ความปลอดภัย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ข้อมูลจะถูกเข้ารหัส</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (Encrypted) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>และจะไม่ปรากฏใน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> Logs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ของ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> GitHub Actions (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>จะขึ้นเป็นเครื่องหมาย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> *** </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t>แทน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">GitHub Secrets </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>go to github &gt; repo &gt; Secrets and variables &gt; action</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">New repository secret </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>CLIENT_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>&gt;  CLIENT_ID from  .env file</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GOOGLE_SHEET_NAME &gt; Receipt Tracker</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GOOGLE_CREDENTIALS &gt; entrie contects of google_credentials.json</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ดูวิธีเขียนโค้ดจาก &gt; https://docs.github.com/ja/actions</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">code .yml to prompt github action </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>schedule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>cron</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'0 0 * * *'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"># Runs every day at 9:00 AM Japan time </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>workflow_dispatch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t># Allows manual trigger from GitHub</t>
+    </r>
+  </si>
+  <si>
+    <t>add more path .github/workflows/ daily_run.yml</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>action : run every day 9:00</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1522,6 +2148,30 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF569CD6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1543,7 +2193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1559,6 +2209,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2450,6 +3107,94 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>45721</xdr:colOff>
+      <xdr:row>217</xdr:row>
+      <xdr:rowOff>140005</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>647701</xdr:colOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>128229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E164D3E-96D1-D3AB-8200-CB74F5D3C104}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="716281" y="49746205"/>
+          <a:ext cx="5295900" cy="1817024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>235</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>242</xdr:row>
+      <xdr:rowOff>13207</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B7905BB-CD36-57E6-1803-968AED4185D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="670560" y="53263801"/>
+          <a:ext cx="5212080" cy="1613406"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2937,7 +3682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L234"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3451,6 +4196,80 @@
     <row r="202" spans="1:2">
       <c r="B202" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>24</v>
+      </c>
+      <c r="B212" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="B213" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="B214" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="B215" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="B216" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="B217" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228">
+        <v>25</v>
+      </c>
+      <c r="B228" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="B229" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="B230" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="B231" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I231" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="B232" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="B233" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="B234" s="12" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3466,7 +4285,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF3FDBC-99E4-40E5-AA7C-C0AF768B925F}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3588,6 +4407,42 @@
     <row r="20" spans="1:2">
       <c r="B20" s="6" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>8</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>9</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" s="5" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
